--- a/CardGameTable/Table/CardDataTable.xlsx
+++ b/CardGameTable/Table/CardDataTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProjects\CardGame\CardGameTable\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A568EE-483A-40EF-BE03-051D9EAECB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EBB33BA-AEC7-4CED-9D8E-95C714E98489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="167">
   <si>
     <t>id</t>
   </si>
@@ -344,10 +344,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>sprint</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>card_effect_buff_movement</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -358,19 +354,209 @@
     <t>card_effect_buff_attack</t>
   </si>
   <si>
-    <t>armor</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>card_effect_damage</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>close shoot</t>
+    <t>card_restore_action</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_buff_attack</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_buff_armor</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_buff_movement</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CONSUME</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_name_restore_action</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_name_buff_attack</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_name_buff_armor</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_name_buff_movement</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_desc_restore_action</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_name_scout_skill1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_name_scout_skill2</t>
+  </si>
+  <si>
+    <t>text_card_name_scout_skill3</t>
+  </si>
+  <si>
+    <t>text_card_name_scout_skill4</t>
+  </si>
+  <si>
+    <t>text_card_name_scout_skill5</t>
+  </si>
+  <si>
+    <t>text_card_name_assult_skill1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_name_assult_skill2</t>
+  </si>
+  <si>
+    <t>text_card_name_assult_skill3</t>
+  </si>
+  <si>
+    <t>text_card_name_assult_skill4</t>
+  </si>
+  <si>
+    <t>text_card_name_assult_skill5</t>
+  </si>
+  <si>
+    <t>text_card_name_heavy_skill1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_name_heavy_skill2</t>
+  </si>
+  <si>
+    <t>text_card_name_heavy_skill3</t>
+  </si>
+  <si>
+    <t>text_card_name_heavy_skill4</t>
+  </si>
+  <si>
+    <t>text_card_name_heavy_skill5</t>
+  </si>
+  <si>
+    <t>text_card_name_specialist_skill1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_name_specialist_skill2</t>
+  </si>
+  <si>
+    <t>text_card_name_specialist_skill3</t>
+  </si>
+  <si>
+    <t>text_card_name_specialist_skill4</t>
+  </si>
+  <si>
+    <t>text_card_name_specialist_skill5</t>
+  </si>
+  <si>
+    <t>text_card_desc_buff_attack</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_desc_buff_armor</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_desc_buff_movement</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_desc_scout_skill1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_desc_scout_skill2</t>
+  </si>
+  <si>
+    <t>text_card_desc_scout_skill3</t>
+  </si>
+  <si>
+    <t>text_card_desc_scout_skill4</t>
+  </si>
+  <si>
+    <t>text_card_desc_scout_skill5</t>
+  </si>
+  <si>
+    <t>text_card_desc_heavy_skill2</t>
+  </si>
+  <si>
+    <t>text_card_desc_heavy_skill3</t>
+  </si>
+  <si>
+    <t>text_card_desc_heavy_skill4</t>
+  </si>
+  <si>
+    <t>text_card_desc_heavy_skill5</t>
+  </si>
+  <si>
+    <t>text_card_desc_specialist_skill2</t>
+  </si>
+  <si>
+    <t>text_card_desc_specialist_skill3</t>
+  </si>
+  <si>
+    <t>text_card_desc_specialist_skill4</t>
+  </si>
+  <si>
+    <t>text_card_desc_specialist_skill5</t>
+  </si>
+  <si>
+    <t>text_card_desc_assult_skill1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_desc_assult_skill2</t>
+  </si>
+  <si>
+    <t>text_card_desc_assult_skill3</t>
+  </si>
+  <si>
+    <t>text_card_desc_assult_skill4</t>
+  </si>
+  <si>
+    <t>text_card_desc_assult_skill5</t>
+  </si>
+  <si>
+    <t>text_card_desc_heavy_skill1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_desc_specialist_skill1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_effect_restore_action</t>
+  </si>
+  <si>
+    <t>card_effect_buff_movement</t>
+  </si>
+  <si>
+    <t>Textures/Card/8</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Textures/Card/3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Textures/Card/35</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Textures/Card/4</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -433,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -448,6 +634,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -666,16 +853,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" customWidth="1"/>
+    <col min="6" max="6" width="29.7109375" customWidth="1"/>
     <col min="12" max="12" width="21.42578125" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
     <col min="15" max="15" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -731,7 +920,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>101</v>
       </c>
@@ -747,7 +936,7 @@
       <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="7" t="s">
         <v>18</v>
       </c>
       <c r="G2" s="2">
@@ -769,7 +958,7 @@
         <v>19</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="N2" s="2">
         <v>5</v>
@@ -779,7 +968,7 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>102</v>
       </c>
@@ -795,7 +984,7 @@
       <c r="E3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="7" t="s">
         <v>18</v>
       </c>
       <c r="G3" s="2">
@@ -827,7 +1016,7 @@
       <c r="Q3" s="2"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>103</v>
       </c>
@@ -843,7 +1032,7 @@
       <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="7" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="2">
@@ -875,7 +1064,7 @@
       <c r="Q4" s="2"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>104</v>
       </c>
@@ -891,7 +1080,7 @@
       <c r="E5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="7" t="s">
         <v>18</v>
       </c>
       <c r="G5" s="2">
@@ -918,7 +1107,7 @@
       <c r="N5" s="2">
         <v>5</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="P5" s="2">
@@ -927,7 +1116,7 @@
       <c r="Q5" s="2"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>105</v>
       </c>
@@ -943,7 +1132,7 @@
       <c r="E6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="7" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="2">
@@ -975,7 +1164,7 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>201</v>
       </c>
@@ -991,7 +1180,7 @@
       <c r="E7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G7" s="3">
@@ -1027,7 +1216,7 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>202</v>
       </c>
@@ -1043,7 +1232,7 @@
       <c r="E8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="7" t="s">
         <v>40</v>
       </c>
       <c r="G8" s="2">
@@ -1071,7 +1260,7 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>203</v>
       </c>
@@ -1087,7 +1276,7 @@
       <c r="E9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="7" t="s">
         <v>44</v>
       </c>
       <c r="G9" s="2">
@@ -1115,7 +1304,7 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>204</v>
       </c>
@@ -1131,7 +1320,7 @@
       <c r="E10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="7" t="s">
         <v>48</v>
       </c>
       <c r="G10" s="2">
@@ -1159,7 +1348,7 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>205</v>
       </c>
@@ -1175,7 +1364,7 @@
       <c r="E11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="7" t="s">
         <v>52</v>
       </c>
       <c r="G11" s="2">
@@ -1203,7 +1392,7 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>206</v>
       </c>
@@ -1219,7 +1408,7 @@
       <c r="E12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G12" s="2">
@@ -1251,7 +1440,7 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>207</v>
       </c>
@@ -1267,7 +1456,7 @@
       <c r="E13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="7" t="s">
         <v>63</v>
       </c>
       <c r="G13" s="2">
@@ -1299,7 +1488,7 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>10001</v>
       </c>
@@ -1315,7 +1504,7 @@
       <c r="E14" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="8" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="2">
@@ -1347,7 +1536,7 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>10002</v>
       </c>
@@ -1363,7 +1552,7 @@
       <c r="E15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="7" t="s">
         <v>73</v>
       </c>
       <c r="G15" s="2">
@@ -1395,7 +1584,7 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>10003</v>
       </c>
@@ -1411,7 +1600,7 @@
       <c r="E16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="8" t="s">
         <v>63</v>
       </c>
       <c r="G16" s="2">
@@ -1443,7 +1632,7 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>10004</v>
       </c>
@@ -1451,7 +1640,7 @@
         <v>77</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>61</v>
@@ -1459,7 +1648,7 @@
       <c r="E17" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="8" t="s">
         <v>79</v>
       </c>
       <c r="G17" s="3">
@@ -1487,164 +1676,188 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2">
-        <v>20101</v>
+    <row r="18" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>10005</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>103</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" s="2">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2">
-        <v>0</v>
-      </c>
-      <c r="K18" s="2">
-        <v>0</v>
+        <v>113</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="N18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2">
-        <v>20102</v>
+        <v>161</v>
+      </c>
+      <c r="N18" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>10006</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>103</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2">
-        <v>0</v>
-      </c>
-      <c r="K19" s="2">
-        <v>0</v>
+        <v>114</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>100</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="N19" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2">
-        <v>20103</v>
+        <v>106</v>
+      </c>
+      <c r="N19" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>10007</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>103</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" s="2">
-        <v>1</v>
-      </c>
-      <c r="H20" s="2">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2">
-        <v>0</v>
-      </c>
-      <c r="K20" s="2">
-        <v>0</v>
+        <v>115</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="N20" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2">
-        <v>20104</v>
+      <c r="N20" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <v>10008</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>103</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G21" s="2">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2">
-        <v>0</v>
-      </c>
-      <c r="K21" s="2">
-        <v>0</v>
+        <v>116</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>165</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="N21" s="2">
+        <v>162</v>
+      </c>
+      <c r="N21" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>20105</v>
+        <v>20101</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>102</v>
@@ -1653,25 +1866,28 @@
         <v>103</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="G22" s="2">
-        <v>1</v>
-      </c>
-      <c r="H22" s="2">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
-        <v>0</v>
-      </c>
-      <c r="K22" s="2">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="N22" s="2">
         <v>1</v>
@@ -1679,19 +1895,22 @@
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>20201</v>
+        <v>20102</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>16</v>
+      <c r="D23" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>111</v>
+        <v>119</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -1703,33 +1922,36 @@
         <v>0</v>
       </c>
       <c r="J23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2">
         <v>0</v>
       </c>
-      <c r="M23" t="s">
-        <v>20</v>
+      <c r="M23" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="N23" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>20202</v>
+        <v>20103</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>16</v>
+      <c r="D24" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>111</v>
+        <v>120</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>143</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -1741,33 +1963,36 @@
         <v>0</v>
       </c>
       <c r="J24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2">
         <v>0</v>
       </c>
-      <c r="M24" t="s">
-        <v>20</v>
+      <c r="M24" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="N24" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>20203</v>
+        <v>20104</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>16</v>
+      <c r="D25" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>111</v>
+        <v>121</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -1779,33 +2004,36 @@
         <v>0</v>
       </c>
       <c r="J25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" s="2">
         <v>0</v>
       </c>
-      <c r="M25" t="s">
-        <v>20</v>
+      <c r="M25" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="N25" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>20204</v>
+        <v>20105</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>16</v>
+      <c r="D26" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>145</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -1817,24 +2045,24 @@
         <v>0</v>
       </c>
       <c r="J26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2">
         <v>0</v>
       </c>
-      <c r="M26" t="s">
-        <v>20</v>
+      <c r="M26" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="N26" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>20205</v>
+        <v>20201</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>102</v>
@@ -1843,7 +2071,10 @@
         <v>16</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>111</v>
+        <v>123</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -1869,19 +2100,22 @@
     </row>
     <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>20301</v>
+        <v>20202</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>108</v>
+      <c r="D28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>155</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -1893,33 +2127,36 @@
         <v>0</v>
       </c>
       <c r="J28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="2">
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>106</v>
-      </c>
-      <c r="N28">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="N28" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>20302</v>
+        <v>20203</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>108</v>
+      <c r="D29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>156</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -1931,33 +2168,36 @@
         <v>0</v>
       </c>
       <c r="J29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" s="2">
         <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>106</v>
-      </c>
-      <c r="N29">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="N29" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>20303</v>
+        <v>20204</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>108</v>
+      <c r="D30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -1969,33 +2209,36 @@
         <v>0</v>
       </c>
       <c r="J30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="2">
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>106</v>
-      </c>
-      <c r="N30">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="N30" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>20304</v>
+        <v>20205</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>108</v>
+      <c r="D31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -2007,24 +2250,24 @@
         <v>0</v>
       </c>
       <c r="J31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="2">
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>106</v>
-      </c>
-      <c r="N31">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="N31" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>20305</v>
+        <v>20301</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>102</v>
@@ -2033,7 +2276,10 @@
         <v>103</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>108</v>
+        <v>128</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>159</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -2051,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N32">
         <v>1</v>
@@ -2059,10 +2305,10 @@
     </row>
     <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>20401</v>
+        <v>20302</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>102</v>
@@ -2071,7 +2317,10 @@
         <v>103</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>109</v>
+        <v>129</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -2089,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N33">
         <v>1</v>
@@ -2097,10 +2346,10 @@
     </row>
     <row r="34" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>20402</v>
+        <v>20303</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>102</v>
@@ -2109,7 +2358,10 @@
         <v>103</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>109</v>
+        <v>130</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -2127,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N34">
         <v>1</v>
@@ -2135,10 +2387,10 @@
     </row>
     <row r="35" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>20403</v>
+        <v>20304</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>102</v>
@@ -2147,7 +2399,10 @@
         <v>103</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>109</v>
+        <v>131</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -2165,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N35">
         <v>1</v>
@@ -2173,10 +2428,10 @@
     </row>
     <row r="36" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>20404</v>
+        <v>20305</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>102</v>
@@ -2185,7 +2440,10 @@
         <v>103</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>109</v>
+        <v>132</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -2203,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N36">
         <v>1</v>
@@ -2211,10 +2469,10 @@
     </row>
     <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>20405</v>
+        <v>20401</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>102</v>
@@ -2223,7 +2481,10 @@
         <v>103</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>109</v>
+        <v>133</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>160</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -2241,9 +2502,173 @@
         <v>0</v>
       </c>
       <c r="M37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>20402</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G38" s="2">
+        <v>1</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0</v>
+      </c>
+      <c r="K38" s="2">
+        <v>0</v>
+      </c>
+      <c r="M38" t="s">
+        <v>106</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
+        <v>20403</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G39" s="2">
+        <v>1</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2">
+        <v>0</v>
+      </c>
+      <c r="K39" s="2">
+        <v>0</v>
+      </c>
+      <c r="M39" t="s">
+        <v>106</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>20404</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="G40" s="2">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2">
+        <v>0</v>
+      </c>
+      <c r="K40" s="2">
+        <v>0</v>
+      </c>
+      <c r="M40" t="s">
+        <v>106</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
+        <v>20405</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G41" s="2">
+        <v>1</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2">
+        <v>0</v>
+      </c>
+      <c r="J41" s="2">
+        <v>0</v>
+      </c>
+      <c r="K41" s="2">
+        <v>0</v>
+      </c>
+      <c r="M41" t="s">
+        <v>106</v>
+      </c>
+      <c r="N41">
         <v>1</v>
       </c>
     </row>
